--- a/data/Endereço Lojas.xlsx
+++ b/data/Endereço Lojas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almavivadobrasil-my.sharepoint.com/personal/ssricardo_almavivadobrasil_com_br/Documents/Trade Marketing - V3/Sabesp/Agente/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almavivadobrasil-my.sharepoint.com/personal/ssricardo_almavivadobrasil_com_br/Documents/Trade Marketing - V3/Sabesp/Agente/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD23D40-9B2E-4329-A1F1-794A23D90519}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EDE67239-4DF0-405F-B03A-9A6C98A96E88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="136">
   <si>
     <t>UN</t>
   </si>
@@ -71,379 +71,379 @@
     <t>Descomplica Capela do Socorro</t>
   </si>
   <si>
-    <t>Rua Cassiano dos Santos, 499 - Jd. Cliper</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 08:00 às 17:00</t>
-  </si>
-  <si>
     <t>Crítica</t>
   </si>
   <si>
     <t>OC</t>
   </si>
   <si>
-    <t>Santo André -AG</t>
-  </si>
-  <si>
     <t>Santo André - AG</t>
   </si>
   <si>
-    <t>Rua Ministro Calogeras, 300</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
     <t>Cajamar</t>
   </si>
   <si>
-    <t>Av. Pedro Celestino L. Penteado, 78</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 09:00 às 15:00</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
     <t>Embu-Guaçu</t>
   </si>
   <si>
-    <t>R. Dr. Rubens de Leite Matos, 60</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 09:00 às 13:00</t>
-  </si>
-  <si>
     <t>São Mateus</t>
   </si>
   <si>
-    <t>Avenida Sapopemba, 16200</t>
-  </si>
-  <si>
     <t>Ribeirão Pires</t>
   </si>
   <si>
-    <t>R. Dr. Nicolau Assef, 290</t>
-  </si>
-  <si>
     <t>OL</t>
   </si>
   <si>
     <t>Guararema</t>
   </si>
   <si>
-    <t>Rua Dr. Falcão, 429</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 8:00 às 12:00</t>
-  </si>
-  <si>
     <t>Rio Grande da Serra</t>
   </si>
   <si>
-    <t>R. José Maria Figueiredo, 256</t>
-  </si>
-  <si>
     <t>Mairiporã</t>
   </si>
   <si>
-    <t>Al. Tibiriçá, 843</t>
-  </si>
-  <si>
     <t>Descomplica Cidade Tiradentes</t>
   </si>
   <si>
-    <t>Estrada Iguatemi, 7001</t>
-  </si>
-  <si>
     <t>OO</t>
   </si>
   <si>
     <t>Vargem Grande Paulista</t>
   </si>
   <si>
-    <t>R. Mário Scarvanci, 111</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 09:00 às 12:00</t>
-  </si>
-  <si>
     <t>Descomplica São Miguel Paulista</t>
   </si>
   <si>
-    <t>Rua Dona Ana Flora Pinheiro de Sousa, 76</t>
-  </si>
-  <si>
     <t>Franco da Rocha</t>
   </si>
   <si>
-    <t>Av. Liberdade, 500</t>
-  </si>
-  <si>
     <t>Juquitiba</t>
   </si>
   <si>
-    <t>Rua da Saudade, 186</t>
-  </si>
-  <si>
     <t>Pirituba</t>
   </si>
   <si>
-    <t>Av. do Anastácio, 2445</t>
-  </si>
-  <si>
     <t>Itaim Paulista</t>
   </si>
   <si>
-    <t>Rua Tibúrcio de Sousa, 1085</t>
-  </si>
-  <si>
     <t>Santana</t>
   </si>
   <si>
-    <t>R. Antônio Pereira de Souza, 110</t>
-  </si>
-  <si>
     <t>Descomplica Butantã</t>
   </si>
   <si>
-    <t>R. Dr. Ulpiano, da Costa Manso, 201</t>
-  </si>
-  <si>
     <t>Descomplica Penha</t>
   </si>
   <si>
-    <t>Rua Candapuí, 492 - Vila Marieta</t>
-  </si>
-  <si>
     <t>Ferraz de Vasconcelos</t>
   </si>
   <si>
-    <t>R. Jacomo Zancheta, 281/285</t>
-  </si>
-  <si>
     <t>M' Boi Mirim</t>
   </si>
   <si>
-    <t>Estr. M' Boi Mirim, 4059</t>
-  </si>
-  <si>
     <t>São Lorenço da serra</t>
   </si>
   <si>
-    <t>Praça Dez de Agosto, 150 - centro</t>
-  </si>
-  <si>
     <t>Poá</t>
   </si>
   <si>
-    <t>Rua Dep. Porfírio da Paz, 8</t>
-  </si>
-  <si>
     <t>Itapecerica da Serra</t>
   </si>
   <si>
-    <t>R. São João, 89</t>
-  </si>
-  <si>
     <t>Francisco Morato</t>
   </si>
   <si>
-    <t>R. Progresso, 902</t>
-  </si>
-  <si>
     <t>Embu das Artes</t>
   </si>
   <si>
-    <t>R. Luis de Almeida Carvalho, 132</t>
-  </si>
-  <si>
     <t>Arujá</t>
   </si>
   <si>
-    <t>R. José Basílio Alvarenga, 78</t>
-  </si>
-  <si>
     <t>Biritiba-Mirim</t>
   </si>
   <si>
-    <t>Av. Reinaldo Benedito de Melo, 157</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 08:00 às 12:00</t>
-  </si>
-  <si>
     <t>Cidade Martins</t>
   </si>
   <si>
-    <t>Av. Manoel Isidoro Martins, 854 - Cidade Martins - Guarulhos - SP, 07132-280</t>
-  </si>
-  <si>
     <t>Salesópolis</t>
   </si>
   <si>
-    <t>Av. Prof. Ademar Bolina, 296</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 13:00 às 17:00</t>
-  </si>
-  <si>
     <t>Santa Isabel</t>
   </si>
   <si>
-    <t>Rua Pref. José Raimundo Lobo, 200</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 8:00 às 17:00</t>
-  </si>
-  <si>
-    <t>Agência Mooca</t>
-  </si>
-  <si>
     <t>Mooca</t>
   </si>
   <si>
-    <t>Rua Sebastião Preto, 192</t>
-  </si>
-  <si>
     <t>Itaquaquecetuba</t>
   </si>
   <si>
-    <t>R. Cornélio Procópio, 201</t>
-  </si>
-  <si>
     <t>Ipiranga</t>
   </si>
   <si>
-    <t>Rua Antônio Marcondes, 81</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arthur Alvim </t>
   </si>
   <si>
-    <t>Artur Alvim</t>
-  </si>
-  <si>
-    <t>Rua Plinio Cavancanti, 151</t>
-  </si>
-  <si>
     <t>Ganha Tempo Barueri</t>
   </si>
   <si>
-    <t>Av. Henriqueta Mendes Guerra, 550 - Centro</t>
-  </si>
-  <si>
     <t>Santana do Parnaíba</t>
   </si>
   <si>
-    <t>R. Alberto Frediani, 27</t>
-  </si>
-  <si>
-    <t>Guarulhos- Câmara Municipal</t>
-  </si>
-  <si>
     <t>Guarulhos - Câmara Municipal</t>
   </si>
   <si>
-    <t>Av. Guarulhos, 845 - Pte. Grande - Guarulhos</t>
-  </si>
-  <si>
     <t>Jardins</t>
   </si>
   <si>
-    <t>Alameda Santos, 1919</t>
-  </si>
-  <si>
     <t>Resolve Fácil Itapevi</t>
   </si>
   <si>
-    <t>Rua José Michelotti, 347 - Cidade da Saude</t>
-  </si>
-  <si>
     <t>Jandira</t>
   </si>
   <si>
-    <t>R. Platão, 59</t>
-  </si>
-  <si>
     <t>Pirapora do Bom Jesus</t>
   </si>
   <si>
-    <t>R. Newton Prado, 20</t>
-  </si>
-  <si>
     <t>Descomplica Mooca</t>
   </si>
   <si>
-    <t>Rua do Hipódromo, 1552</t>
-  </si>
-  <si>
     <t>Descomplica Parelheiros</t>
   </si>
   <si>
-    <t>Estr. Ecoturística de Parelheiros, 5252</t>
-  </si>
-  <si>
     <t xml:space="preserve">Major Rugde </t>
   </si>
   <si>
-    <t>Major Rugde</t>
-  </si>
-  <si>
     <t>RUA MAJOR RUDGE, 37 - SAO PAULO/SP</t>
   </si>
   <si>
-    <t xml:space="preserve">Freguesia do Ó </t>
-  </si>
-  <si>
     <t>Freguesia do Ó</t>
   </si>
   <si>
-    <t>Rua José Soriano de Sousa, 297</t>
-  </si>
-  <si>
     <t>Descomplica Campo Limpo</t>
   </si>
   <si>
-    <t>Avenida Giovanni Gronchi, 7143 – Vila Andrade</t>
-  </si>
-  <si>
     <t>Fácil Shopping Bonsucesso</t>
   </si>
   <si>
-    <t>Av. Juscelino Kubitschek de Oliveira, 5308 (Shopping Bonsucesso)</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 08:00 às 17:00 Sábado 8:00 às 13:00</t>
-  </si>
-  <si>
     <t>Chacara Santo Antonio</t>
   </si>
   <si>
-    <t>Mais Shopping - Rua Amador Bueno, 229, 2º andar - Santo Amaro - São Paulo</t>
-  </si>
-  <si>
     <t>Polo Taboão da Serra</t>
   </si>
   <si>
-    <t>Rua João Meneghette, 300</t>
-  </si>
-  <si>
     <t>Gopoúva</t>
   </si>
   <si>
-    <t>Av Emilio Ribas, 1247</t>
-  </si>
-  <si>
-    <t>Caieiras</t>
-  </si>
-  <si>
-    <t>Rua Amleto Ricciarelli, 81</t>
-  </si>
-  <si>
-    <t>Segunda a Sexta 08:00 às 16:00</t>
+    <t xml:space="preserve"> Caieiras</t>
+  </si>
+  <si>
+    <t>Pinheiros - SEDE (Backoffice)</t>
+  </si>
+  <si>
+    <t>ALAMEDA SANTOS, 1919 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA ANTONIO MARCONDES, 81 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA SAPOPEMBA, 16200 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA SEBASTIAO PRETO, 192 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA MINISTRO CALOGERAS, 300 - SANTO ANDRE/SP</t>
+  </si>
+  <si>
+    <t>RUA HIPODROMO, 1552 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sede Sabesp Pinheiro </t>
+  </si>
+  <si>
+    <t>RUA JOSE BASILIO ALVARENGA, 78 - ARUJA/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA REINALDO BENEDITO DE MELO, 157 - BIRITIBA-MIRIM/SP</t>
+  </si>
+  <si>
+    <t>RUA JACOMO ZANCHETA, 285 - FERRAZ DE VASCONCELOS/SP</t>
+  </si>
+  <si>
+    <t>RUA CORNELIO PROCOPIO, 201 - ITAQUAQUECETUBA/SP</t>
+  </si>
+  <si>
+    <t>RUA DEPUTADO PORFIRIO DA PAZ, 8 - POA/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA PROFESSOR ADEMAR BOLINA, 296 - SALESOPOLIS/SP</t>
+  </si>
+  <si>
+    <t>RUA TIBURCIO DE SOUZA, 1085 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA DONA ANA FLORA PINHEIRO DE SOUZA, 76 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA CANDAPUI, 492 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>ESTRADA IGUATEMI, 7001 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA PREFEITO JOSE RAIMUNDO LOBO, 200 - SANTA ISABEL/SP</t>
+  </si>
+  <si>
+    <t>RUA DOUTOR FALCAO, 429 - GUARAREMA/SP</t>
+  </si>
+  <si>
+    <t>RUA PLÍNIO CAVALCANTI, 153 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA CAIXA DA AGUA, 14 - GUARULHOS/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA ITABERABA, 185 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA DO ANASTACIO, 2445 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA VIRGILIO MARTINS DE OLIVEIRA, 233 - FRANCISCO MORATO/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA LIBERDADE, 500 - FRANCO DA ROCHA/SP</t>
+  </si>
+  <si>
+    <t>RUA ANTONIO PEREIRA DE SOUSA, 110 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA PEDRO CELESTINO LEITE PENTEADO, 78 - CAJAMAR/SP</t>
+  </si>
+  <si>
+    <t>ALAMEDA TIBIRICA, 843 - MAIRIPORA/SP</t>
+  </si>
+  <si>
+    <t>Av. Manoel Isidoro Martins, 854 - Cidade Martins, Guarulhos</t>
+  </si>
+  <si>
+    <t>ESTRADA PRESIDENTE JUSCELINO K OLIVEIRA, 5308 - GUARULHOS/SP - 7244000</t>
+  </si>
+  <si>
+    <t>Rua Amleto Ricciarelli, 81 – Centro, Caieiras – SP</t>
+  </si>
+  <si>
+    <t>AVENIDA GUARULHOS, 845 - GUARULHOS/SP</t>
+  </si>
+  <si>
+    <t>RUA PROFESSOR VALDECIR CAMPESTRE, 268 - VARGEM GRANDE PAULISTA/SP</t>
+  </si>
+  <si>
+    <t>RUA PLATAO, 59 - JANDIRA/SP</t>
+  </si>
+  <si>
+    <t>RUA NEWTON PRADO, 20 - PIRAPORA DO BOM JESUS/SP</t>
+  </si>
+  <si>
+    <t>RUA ALBERTO FREDIANI, 27 - SANTANA DE PARNAIBA/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA HENRIQUETA MENDES GUERRA, 550 - BARUERI/SP</t>
+  </si>
+  <si>
+    <t>RUA DOUTOR ULPIANO DA COSTA MANSO, 201 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>AVENIDA ALFRIED KRUPP, 2000 - CAMPO LIMPO PAULISTA/SP</t>
+  </si>
+  <si>
+    <t>RUA JOSE MICHELOTTI, 88 - ITAPEVI/SP</t>
+  </si>
+  <si>
+    <t>RUA JOAO MENEGUETTI, 300 - TABOAO DA SERRA/SP</t>
+  </si>
+  <si>
+    <t>RUA LUIZ DE ALMEIDA CARVALHO, 132 - EMBU DAS ARTES/SP</t>
+  </si>
+  <si>
+    <t>RUA SÃO JOAO, 89 - ITAPECERICA DA SERRA/SP</t>
+  </si>
+  <si>
+    <t>ESTRADA M BOI MIRIM, 4059 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA DOUTOR NICOLAU ASSEF, 290 - RIBEIRAO PIRES/SP</t>
+  </si>
+  <si>
+    <t>RUA JOSE MARIA DE FIGUEIREDO, 256 - RIO GRANDE DA SERRA/SP</t>
+  </si>
+  <si>
+    <t>RUA DOUTOR RUBENS LEITE DE MATOS, 60 - EMBU-GUACU/SP</t>
+  </si>
+  <si>
+    <t>RUA AMERICO BRASILIENSE, 700 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA CASSIANO DOS SANTOS, 499 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>RUA DA SAUDADE, 186 - JUQUITIBA/SP</t>
+  </si>
+  <si>
+    <t>PRAÇA DEZ DE AGOSTO, 150 - SAO LOURENCO DA SERRA/SP</t>
+  </si>
+  <si>
+    <t>ESTRADA ECOTURISTICA DE PARELHEIROS, 5252 - SAO PAULO/SP</t>
+  </si>
+  <si>
+    <t>8H AS 16H</t>
+  </si>
+  <si>
+    <t>8H AS 17H (Sab: 08h as 12h)</t>
+  </si>
+  <si>
+    <t>8H AS 17H</t>
+  </si>
+  <si>
+    <t>8H AS 11H</t>
+  </si>
+  <si>
+    <t>13H AS 16H</t>
+  </si>
+  <si>
+    <t>8H AS 12H</t>
+  </si>
+  <si>
+    <t>8H AS 16H (SEMANA) E 8H AS 13H (SÁBADO)</t>
+  </si>
+  <si>
+    <t>9H AS 15H</t>
+  </si>
+  <si>
+    <t>9H AS 14H</t>
+  </si>
+  <si>
+    <t>9H AS 12H</t>
+  </si>
+  <si>
+    <t>8H AS 14H</t>
+  </si>
+  <si>
+    <t>7H AS 18H (SEMANA) E 7H AS 12H (SÁBADO)</t>
+  </si>
+  <si>
+    <t>10H AS 15H</t>
+  </si>
+  <si>
+    <t>10H AS 13H</t>
   </si>
 </sst>
 </file>
@@ -815,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064F706F-093A-476A-A2B2-72479FD1CD39}">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -859,251 +859,259 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>SUM(F2:G2)</f>
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H54" si="0">SUM(F3:G3)</f>
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>9</v>
-      </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="F10">
         <v>4</v>
@@ -1112,305 +1120,316 @@
         <v>0</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="I15" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16">
         <v>12</v>
       </c>
-      <c r="F16">
-        <v>10</v>
-      </c>
       <c r="G16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17">
         <v>12</v>
       </c>
-      <c r="F17">
-        <v>11</v>
-      </c>
       <c r="G17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
         <v>60</v>
@@ -1422,338 +1441,350 @@
         <v>61</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="I21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23">
         <v>12</v>
       </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>4</v>
       </c>
       <c r="H25">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F26">
-        <v>8</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>8</v>
-      </c>
       <c r="I26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27">
         <v>9</v>
       </c>
-      <c r="B27" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>73</v>
-      </c>
-      <c r="E27" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27">
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G27">
-        <v>4</v>
-      </c>
-      <c r="H27">
-        <v>14</v>
-      </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="I30" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1761,347 +1792,359 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="F33">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I33" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="D36" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="F37">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="H37">
-        <v>13</v>
-      </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="D39" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F39">
-        <v>2</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>2</v>
-      </c>
       <c r="I39" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
         <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="F42">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
         <v>110</v>
       </c>
-      <c r="C43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
-      </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B44" t="s">
-        <v>112</v>
-      </c>
-      <c r="C44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" t="s">
-        <v>113</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44">
-        <v>5</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>5</v>
-      </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2109,144 +2152,149 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="F45">
         <v>6</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="F46">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="C47" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="F47">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I47" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E49" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2254,115 +2302,149 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E50" t="s">
+        <v>133</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="F50">
-        <v>9</v>
-      </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50">
-        <v>9</v>
-      </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="F51">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E52" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F52">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="D53" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E53" t="s">
         <v>135</v>
       </c>
       <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I53" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
+        <v>59</v>
+      </c>
+      <c r="C54" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" t="s">
+        <v>124</v>
+      </c>
+      <c r="F54">
         <v>7</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I53" t="s">
-        <v>22</v>
+      <c r="I54" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/Endereço Lojas.xlsx
+++ b/data/Endereço Lojas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almavivadobrasil-my.sharepoint.com/personal/ssricardo_almavivadobrasil_com_br/Documents/Trade Marketing - V3/Sabesp/Agente/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CD23D40-9B2E-4329-A1F1-794A23D90519}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4836199-7AD5-425A-8AAF-260BCEF2F887}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EDE67239-4DF0-405F-B03A-9A6C98A96E88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="143">
   <si>
     <t>UN</t>
   </si>
@@ -77,9 +77,6 @@
     <t>OC</t>
   </si>
   <si>
-    <t>Santo André - AG</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
@@ -218,232 +215,256 @@
     <t>Descomplica Parelheiros</t>
   </si>
   <si>
-    <t xml:space="preserve">Major Rugde </t>
-  </si>
-  <si>
-    <t>RUA MAJOR RUDGE, 37 - SAO PAULO/SP</t>
-  </si>
-  <si>
     <t>Freguesia do Ó</t>
   </si>
   <si>
     <t>Descomplica Campo Limpo</t>
   </si>
   <si>
-    <t>Fácil Shopping Bonsucesso</t>
-  </si>
-  <si>
     <t>Chacara Santo Antonio</t>
   </si>
   <si>
     <t>Polo Taboão da Serra</t>
   </si>
   <si>
-    <t>Gopoúva</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Caieiras</t>
   </si>
   <si>
     <t>Pinheiros - SEDE (Backoffice)</t>
   </si>
   <si>
-    <t>ALAMEDA SANTOS, 1919 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA ANTONIO MARCONDES, 81 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA SAPOPEMBA, 16200 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA SEBASTIAO PRETO, 192 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA MINISTRO CALOGERAS, 300 - SANTO ANDRE/SP</t>
-  </si>
-  <si>
-    <t>RUA HIPODROMO, 1552 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sede Sabesp Pinheiro </t>
-  </si>
-  <si>
-    <t>RUA JOSE BASILIO ALVARENGA, 78 - ARUJA/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA REINALDO BENEDITO DE MELO, 157 - BIRITIBA-MIRIM/SP</t>
-  </si>
-  <si>
-    <t>RUA JACOMO ZANCHETA, 285 - FERRAZ DE VASCONCELOS/SP</t>
-  </si>
-  <si>
-    <t>RUA CORNELIO PROCOPIO, 201 - ITAQUAQUECETUBA/SP</t>
-  </si>
-  <si>
-    <t>RUA DEPUTADO PORFIRIO DA PAZ, 8 - POA/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA PROFESSOR ADEMAR BOLINA, 296 - SALESOPOLIS/SP</t>
-  </si>
-  <si>
-    <t>RUA TIBURCIO DE SOUZA, 1085 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA DONA ANA FLORA PINHEIRO DE SOUZA, 76 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA CANDAPUI, 492 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>ESTRADA IGUATEMI, 7001 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA PREFEITO JOSE RAIMUNDO LOBO, 200 - SANTA ISABEL/SP</t>
-  </si>
-  <si>
-    <t>RUA DOUTOR FALCAO, 429 - GUARAREMA/SP</t>
-  </si>
-  <si>
-    <t>RUA PLÍNIO CAVALCANTI, 153 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA CAIXA DA AGUA, 14 - GUARULHOS/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA ITABERABA, 185 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA DO ANASTACIO, 2445 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA VIRGILIO MARTINS DE OLIVEIRA, 233 - FRANCISCO MORATO/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA LIBERDADE, 500 - FRANCO DA ROCHA/SP</t>
-  </si>
-  <si>
-    <t>RUA ANTONIO PEREIRA DE SOUSA, 110 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA PEDRO CELESTINO LEITE PENTEADO, 78 - CAJAMAR/SP</t>
-  </si>
-  <si>
-    <t>ALAMEDA TIBIRICA, 843 - MAIRIPORA/SP</t>
-  </si>
-  <si>
     <t>Av. Manoel Isidoro Martins, 854 - Cidade Martins, Guarulhos</t>
   </si>
   <si>
-    <t>ESTRADA PRESIDENTE JUSCELINO K OLIVEIRA, 5308 - GUARULHOS/SP - 7244000</t>
-  </si>
-  <si>
-    <t>Rua Amleto Ricciarelli, 81 – Centro, Caieiras – SP</t>
-  </si>
-  <si>
-    <t>AVENIDA GUARULHOS, 845 - GUARULHOS/SP</t>
-  </si>
-  <si>
-    <t>RUA PROFESSOR VALDECIR CAMPESTRE, 268 - VARGEM GRANDE PAULISTA/SP</t>
-  </si>
-  <si>
-    <t>RUA PLATAO, 59 - JANDIRA/SP</t>
-  </si>
-  <si>
-    <t>RUA NEWTON PRADO, 20 - PIRAPORA DO BOM JESUS/SP</t>
-  </si>
-  <si>
-    <t>RUA ALBERTO FREDIANI, 27 - SANTANA DE PARNAIBA/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA HENRIQUETA MENDES GUERRA, 550 - BARUERI/SP</t>
-  </si>
-  <si>
-    <t>RUA DOUTOR ULPIANO DA COSTA MANSO, 201 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>AVENIDA ALFRIED KRUPP, 2000 - CAMPO LIMPO PAULISTA/SP</t>
-  </si>
-  <si>
-    <t>RUA JOSE MICHELOTTI, 88 - ITAPEVI/SP</t>
-  </si>
-  <si>
-    <t>RUA JOAO MENEGUETTI, 300 - TABOAO DA SERRA/SP</t>
-  </si>
-  <si>
-    <t>RUA LUIZ DE ALMEIDA CARVALHO, 132 - EMBU DAS ARTES/SP</t>
-  </si>
-  <si>
-    <t>RUA SÃO JOAO, 89 - ITAPECERICA DA SERRA/SP</t>
-  </si>
-  <si>
-    <t>ESTRADA M BOI MIRIM, 4059 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA DOUTOR NICOLAU ASSEF, 290 - RIBEIRAO PIRES/SP</t>
-  </si>
-  <si>
-    <t>RUA JOSE MARIA DE FIGUEIREDO, 256 - RIO GRANDE DA SERRA/SP</t>
-  </si>
-  <si>
-    <t>RUA DOUTOR RUBENS LEITE DE MATOS, 60 - EMBU-GUACU/SP</t>
-  </si>
-  <si>
-    <t>RUA AMERICO BRASILIENSE, 700 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA CASSIANO DOS SANTOS, 499 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>RUA DA SAUDADE, 186 - JUQUITIBA/SP</t>
-  </si>
-  <si>
-    <t>PRAÇA DEZ DE AGOSTO, 150 - SAO LOURENCO DA SERRA/SP</t>
-  </si>
-  <si>
-    <t>ESTRADA ECOTURISTICA DE PARELHEIROS, 5252 - SAO PAULO/SP</t>
-  </si>
-  <si>
-    <t>8H AS 16H</t>
-  </si>
-  <si>
-    <t>8H AS 17H (Sab: 08h as 12h)</t>
-  </si>
-  <si>
-    <t>8H AS 17H</t>
-  </si>
-  <si>
-    <t>8H AS 11H</t>
-  </si>
-  <si>
-    <t>13H AS 16H</t>
-  </si>
-  <si>
-    <t>8H AS 12H</t>
-  </si>
-  <si>
-    <t>8H AS 16H (SEMANA) E 8H AS 13H (SÁBADO)</t>
-  </si>
-  <si>
-    <t>9H AS 15H</t>
-  </si>
-  <si>
-    <t>9H AS 14H</t>
-  </si>
-  <si>
-    <t>9H AS 12H</t>
-  </si>
-  <si>
-    <t>8H AS 14H</t>
-  </si>
-  <si>
-    <t>7H AS 18H (SEMANA) E 7H AS 12H (SÁBADO)</t>
-  </si>
-  <si>
-    <t>10H AS 15H</t>
-  </si>
-  <si>
-    <t>10H AS 13H</t>
+    <t>Coordenador</t>
+  </si>
+  <si>
+    <t>Santo André</t>
+  </si>
+  <si>
+    <t>Penha</t>
+  </si>
+  <si>
+    <t>Vila Galvão</t>
+  </si>
+  <si>
+    <t>CIC Guarulhos</t>
+  </si>
+  <si>
+    <t>Casa Verde</t>
+  </si>
+  <si>
+    <t>Cotia</t>
+  </si>
+  <si>
+    <t>São Bernardo Do Campo</t>
+  </si>
+  <si>
+    <t>Alameda Santos, 1919 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Antonio Marcondes, 81 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Sapopemba, 16200 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Sebastiao Preto, 192 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Ministro Calogeras, 300 - Santo Andre/Sp</t>
+  </si>
+  <si>
+    <t>Rua Hipodromo, 1552 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Sede Sabesp Pinheiro</t>
+  </si>
+  <si>
+    <t>Rua Jose Basilio Alvarenga, 78 - Aruja/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Reinaldo Benedito De Melo, 157 - Biritiba-Mirim/Sp</t>
+  </si>
+  <si>
+    <t>Rua Jacomo Zancheta, 285 - Ferraz De Vasconcelos/Sp</t>
+  </si>
+  <si>
+    <t>Rua Cornelio Procopio, 201 - Itaquaquecetuba/Sp</t>
+  </si>
+  <si>
+    <t>Rua Deputado Porfirio Da Paz, 8 - Poa/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Professor Ademar Bolina, 296 - Salesopolis/Sp</t>
+  </si>
+  <si>
+    <t>Rua Tiburcio De Souza, 1085 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Dona Ana Flora Pinheiro De Souza, 76 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Candapui, 492 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Estrada Iguatemi, 7001 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Prefeito Jose Raimundo Lobo, 200 - Santa Isabel/Sp</t>
+  </si>
+  <si>
+    <t>Rua Doutor Falcao, 429 - Guararema/Sp</t>
+  </si>
+  <si>
+    <t>Rua Major Rudge, 37 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Plínio Cavalcanti, 153 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Caixa Da Agua, 14 - Guarulhos/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Itaberaba, 185 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Do Anastacio, 2445 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Virgilio Martins De Oliveira, 233 - Francisco Morato/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Liberdade, 500 - Franco Da Rocha/Sp</t>
+  </si>
+  <si>
+    <t>Rua Antonio Pereira De Sousa, 110 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Pedro Celestino Leite Penteado, 78 - Cajamar/Sp</t>
+  </si>
+  <si>
+    <t>Alameda Tibirica, 843 - Mairipora/Sp</t>
+  </si>
+  <si>
+    <t>Estrada Presidente Juscelino K Oliveira, 5308 - Guarulhos/Sp - 7244000</t>
+  </si>
+  <si>
+    <t>Rua Amleto Ricciarelli, 81 – Centro, Caieiras – Sp</t>
+  </si>
+  <si>
+    <t>Avenida Guarulhos, 845 - Guarulhos/Sp</t>
+  </si>
+  <si>
+    <t>Rua Professor Valdecir Campestre, 268 - Vargem Grande Paulista/Sp</t>
+  </si>
+  <si>
+    <t>Rua Platao, 59 - Jandira/Sp</t>
+  </si>
+  <si>
+    <t>Rua Newton Prado, 20 - Pirapora Do Bom Jesus/Sp</t>
+  </si>
+  <si>
+    <t>Rua Alberto Frediani, 27 - Santana De Parnaiba/Sp</t>
+  </si>
+  <si>
+    <t>Avenida Henriqueta Mendes Guerra, 550 - Barueri/Sp</t>
+  </si>
+  <si>
+    <t>Rua Doutor Ulpiano Da Costa Manso, 201 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Av. Giovanni Gronchi, 7143 - 1° Andar - Vila Andrade, São Paulo - Sp, 05724-005</t>
+  </si>
+  <si>
+    <t>Rua Jose Michelotti, 88 - Itapevi/Sp</t>
+  </si>
+  <si>
+    <t>Rua Joao Meneguetti, 300 - Taboao Da Serra/Sp</t>
+  </si>
+  <si>
+    <t>Rua Luiz De Almeida Carvalho, 132 - Embu Das Artes/Sp</t>
+  </si>
+  <si>
+    <t>Rua São Joao, 89 - Itapecerica Da Serra/Sp</t>
+  </si>
+  <si>
+    <t>Estrada M Boi Mirim, 4059 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Doutor Nicolau Assef, 290 - Ribeirao Pires/Sp</t>
+  </si>
+  <si>
+    <t>Rua Jose Maria De Figueiredo, 256 - Rio Grande Da Serra/Sp</t>
+  </si>
+  <si>
+    <t>Rua Doutor Rubens Leite De Matos, 60 - Embu-Guacu/Sp</t>
+  </si>
+  <si>
+    <t>Rua Americo Brasiliense, 700 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Cassiano Dos Santos, 499 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua Da Saudade, 186 - Juquitiba/Sp</t>
+  </si>
+  <si>
+    <t>Praça Dez De Agosto, 150 - Sao Lourenco Da Serra/Sp</t>
+  </si>
+  <si>
+    <t>Estrada Ecoturistica De Parelheiros, 5252 - Sao Paulo/Sp</t>
+  </si>
+  <si>
+    <t>Rua José Soriano De Sousa, 297 - Casa Verde Alta, São Paulo - Sp, 02555-050</t>
+  </si>
+  <si>
+    <t>Avenida Nossa Senhora De Fatima, 845 - Cotia/Sp - 6717210</t>
+  </si>
+  <si>
+    <t>Rua Paulo Di Favari, 60 - Sao Bernardo Do Campo/Sp - 09618100</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 08:00 às 16:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 08:00 às 17:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 8:00 às 11:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 13:00 às 16:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 08:00 às 12:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 08:00 às 16:00 Sábado 8:00 às 13:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 09:00 às 15:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 09:00 às 14:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 09:00 às 13:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 09:00 às 12:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 07:00 às 18:00 Sábado 7:00 às 12:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 10:00 às 15:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 10:00 às 13:00</t>
+  </si>
+  <si>
+    <t>Segunda a Sexta 07:00 às 19:00 Sábado 7:00 às 13:00</t>
   </si>
 </sst>
 </file>
@@ -815,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064F706F-093A-476A-A2B2-72479FD1CD39}">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -828,7 +849,7 @@
     <col min="9" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -856,52 +877,58 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
         <f>SUM(F2:G2)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -910,28 +937,31 @@
         <v>2</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H54" si="0">SUM(F3:G3)</f>
+        <f t="shared" ref="H3:H57" si="0">SUM(F3:G3)</f>
         <v>15</v>
       </c>
       <c r="I3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F4">
         <v>23</v>
@@ -946,22 +976,25 @@
       <c r="I4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -976,172 +1009,190 @@
       <c r="I5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
       <c r="I7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F9">
-        <v>6</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
       <c r="I10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1156,22 +1207,25 @@
       <c r="I11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1186,82 +1240,91 @@
       <c r="I12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
       <c r="I13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
       <c r="I14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F15">
         <v>16</v>
@@ -1276,202 +1339,223 @@
       <c r="I15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17">
+        <v>11</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="C20" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F17">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18">
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
+        <v>133</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21">
         <v>6</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19">
-        <v>5</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="I20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21">
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
       <c r="I21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -1486,22 +1570,25 @@
       <c r="I22" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F23">
         <v>12</v>
@@ -1516,52 +1603,58 @@
       <c r="I23" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>4</v>
       </c>
       <c r="H24">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I24" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E25" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F25">
         <v>13</v>
@@ -1576,82 +1669,91 @@
       <c r="I25" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
       <c r="I27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F28">
         <v>18</v>
@@ -1666,22 +1768,25 @@
       <c r="I28" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>15</v>
-      </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -1694,294 +1799,324 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F32">
+        <v>8</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" t="s">
+        <v>129</v>
+      </c>
+      <c r="F33">
+        <v>8</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" t="s">
-        <v>68</v>
-      </c>
-      <c r="C33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s">
-        <v>100</v>
-      </c>
-      <c r="E33" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33">
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36">
+        <v>6</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" t="s">
+        <v>108</v>
+      </c>
+      <c r="E37" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" t="s">
+        <v>109</v>
+      </c>
+      <c r="E38" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38">
+        <v>8</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I33" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34">
-        <v>3</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="I34" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" t="s">
-        <v>127</v>
-      </c>
-      <c r="F35">
-        <v>9</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B36" t="s">
-        <v>56</v>
-      </c>
-      <c r="C36" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" t="s">
         <v>130</v>
-      </c>
-      <c r="F36">
-        <v>7</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="I36" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>25</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37">
-        <v>4</v>
-      </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I37" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D38" t="s">
-        <v>105</v>
-      </c>
-      <c r="E38" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38">
-        <v>9</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" t="s">
-        <v>124</v>
       </c>
       <c r="F39">
         <v>11</v>
@@ -1996,142 +2131,157 @@
       <c r="I39" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E41" t="s">
         <v>130</v>
       </c>
       <c r="F41">
+        <v>4</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
       <c r="I41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E42" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
       <c r="I42" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
       <c r="I43" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E44" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F44">
         <v>12</v>
@@ -2146,22 +2296,25 @@
       <c r="I44" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E45" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F45">
         <v>6</v>
@@ -2176,142 +2329,157 @@
       <c r="I45" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F46">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G46">
         <v>4</v>
       </c>
       <c r="H46">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E47" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F47">
+        <v>5</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
       <c r="I47" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J47">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D48" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
       <c r="I48" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J48">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E49" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
       <c r="I49" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J49">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D50" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F50">
         <v>11</v>
@@ -2326,8 +2494,11 @@
       <c r="I50" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -2338,10 +2509,10 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F51">
         <v>8</v>
@@ -2356,95 +2527,206 @@
       <c r="I51" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E52" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
       <c r="I53" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E54" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G54">
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+      <c r="D55" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" t="s">
+        <v>129</v>
+      </c>
+      <c r="F55">
+        <v>8</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55">
         <v>0</v>
       </c>
-      <c r="H54">
-        <f t="shared" si="0"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" t="s">
+        <v>129</v>
+      </c>
+      <c r="F56">
         <v>7</v>
       </c>
-      <c r="I54" t="s">
-        <v>16</v>
+      <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" t="s">
+        <v>128</v>
+      </c>
+      <c r="E57" t="s">
+        <v>142</v>
+      </c>
+      <c r="F57">
+        <v>15</v>
+      </c>
+      <c r="G57">
+        <v>5</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Endereço Lojas.xlsx
+++ b/data/Endereço Lojas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://almavivadobrasil-my.sharepoint.com/personal/ssricardo_almavivadobrasil_com_br/Documents/Trade Marketing - V3/Sabesp/Agente/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4836199-7AD5-425A-8AAF-260BCEF2F887}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{EE3AA4AF-4D2C-4EBE-BA0D-2617FE600E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C8CC0B0-5DC1-4BE6-9DCF-36C640452098}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{EDE67239-4DF0-405F-B03A-9A6C98A96E88}"/>
   </bookViews>
@@ -517,6 +517,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1096,17 +1100,17 @@
         <v>129</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="I8">
         <v>0</v>
-      </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
       </c>
       <c r="J8">
         <v>2</v>
